--- a/checklist_forms/028_emergency_assembly_checklist--checklist_forms.xlsx
+++ b/checklist_forms/028_emergency_assembly_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire'}</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fire'}</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'injury'}</t>
+          <t>injury</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Injury'}</t>
+          <t>Injury</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'inside'}</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Inside'}</t>
+          <t>Inside</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'outside'}</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Outside'}</t>
+          <t>Outside</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
